--- a/public/exports-from-60/29188475.xlsx
+++ b/public/exports-from-60/29188475.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526270</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526267</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562929</t>
+          <t xml:space="preserve">311562930</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -13339,12 +13339,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562929</t>
+          <t xml:space="preserve">311562931</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562920</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562925</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -13789,12 +13789,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562915</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562916</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -13939,12 +13939,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562926</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562918</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562919</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M188" t="inlineStr">

--- a/public/exports-from-60/29188475.xlsx
+++ b/public/exports-from-60/29188475.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526272</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526266</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526267</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562922</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562930</t>
+          <t xml:space="preserve">311562932</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -13339,12 +13339,12 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562931</t>
+          <t xml:space="preserve">311562932</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562912</t>
+          <t xml:space="preserve">311562928</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562920</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562913</t>
+          <t xml:space="preserve">311562928</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -13714,12 +13714,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562914</t>
+          <t xml:space="preserve">311562928</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -13789,12 +13789,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562915</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562916</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562918</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -14089,12 +14089,12 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562919</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -14164,12 +14164,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562924</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">

--- a/public/exports-from-60/29188475.xlsx
+++ b/public/exports-from-60/29188475.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526272</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526266</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526270</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562922</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562932</t>
+          <t xml:space="preserve">311562929</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562932</t>
+          <t xml:space="preserve">311562929</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562928</t>
+          <t xml:space="preserve">311562912</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562928</t>
+          <t xml:space="preserve">311562913</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562925</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -13714,12 +13714,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562928</t>
+          <t xml:space="preserve">311562914</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -13939,12 +13939,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562926</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -14164,12 +14164,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562924</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M189" t="inlineStr">
